--- a/docs/график работ типовго  проекта.xlsx
+++ b/docs/график работ типовго  проекта.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Отедел Системного Анализа\1. Audit Manager\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69D8EE3B-B791-47E6-8571-DF3790BF2956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355B28E3-4758-43BA-9487-AA51D6877408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Оценка аудита" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Оценка аудита'!$A$1:$K$86</definedName>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="152">
   <si>
     <t>#</t>
   </si>
@@ -54,9 +55,6 @@
     <t>GPT-5.4, $</t>
   </si>
   <si>
-    <t>Статус</t>
-  </si>
-  <si>
     <t>Нед 1</t>
   </si>
   <si>
@@ -492,7 +490,7 @@
     <t>Лимит: 17,000K / неделю</t>
   </si>
   <si>
-    <t>Чел/дней</t>
+    <t>Чел/дн</t>
   </si>
 </sst>
 </file>
@@ -1018,6 +1016,55 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>134390</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>76902</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82F72486-D94D-4FF5-BD1A-BA61F9A802FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7449590" cy="5029902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1303,6 +1350,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:P86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1311,8 +1361,9 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="15" width="9" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" customWidth="1"/>
+    <col min="8" max="11" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1334,38 +1385,36 @@
       <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="47" t="s">
+      <c r="G1" s="47"/>
+      <c r="H1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="47" t="s">
+      <c r="I1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="47" t="s">
+      <c r="J1" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="47" t="s">
+      <c r="K1" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="47" t="s">
-        <v>10</v>
-      </c>
       <c r="L1" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M1" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N1" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O1" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -1381,18 +1430,18 @@
       <c r="N2" s="44"/>
       <c r="O2" s="44"/>
     </row>
-    <row r="3" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="E3" s="9">
         <v>2653</v>
@@ -1401,7 +1450,7 @@
         <v>6.48</v>
       </c>
       <c r="G3" s="58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="27">
         <v>2653</v>
@@ -1414,18 +1463,18 @@
       <c r="N3" s="43"/>
       <c r="O3" s="43"/>
     </row>
-    <row r="4" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="E4" s="9">
         <v>1991</v>
@@ -1434,7 +1483,7 @@
         <v>3.6</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H4" s="11">
         <v>1991</v>
@@ -1447,18 +1496,18 @@
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
     </row>
-    <row r="5" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="E5" s="9">
         <v>999</v>
@@ -1467,7 +1516,7 @@
         <v>1.26</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H5" s="11">
         <v>999</v>
@@ -1480,18 +1529,18 @@
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
     </row>
-    <row r="6" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="9">
         <v>1025</v>
@@ -1500,7 +1549,7 @@
         <v>1.44</v>
       </c>
       <c r="G6" s="60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="22">
         <v>1025</v>
@@ -1513,14 +1562,14 @@
       <c r="N6" s="23"/>
       <c r="O6" s="23"/>
     </row>
-    <row r="7" spans="1:15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="16">
         <v>6668</v>
@@ -1546,7 +1595,7 @@
     <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -1562,18 +1611,18 @@
       <c r="N8" s="44"/>
       <c r="O8" s="44"/>
     </row>
-    <row r="9" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="E9" s="9">
         <v>1253</v>
@@ -1582,7 +1631,7 @@
         <v>2.34</v>
       </c>
       <c r="G9" s="61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H9" s="27">
         <v>1253</v>
@@ -1595,18 +1644,18 @@
       <c r="N9" s="43"/>
       <c r="O9" s="43"/>
     </row>
-    <row r="10" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>30</v>
       </c>
       <c r="E10" s="9">
         <v>751</v>
@@ -1615,7 +1664,7 @@
         <v>0.72</v>
       </c>
       <c r="G10" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" s="11">
         <v>751</v>
@@ -1628,18 +1677,18 @@
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
     </row>
-    <row r="11" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="E11" s="9">
         <v>858</v>
@@ -1648,7 +1697,7 @@
         <v>1.08</v>
       </c>
       <c r="G11" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11" s="11">
         <v>858</v>
@@ -1661,18 +1710,18 @@
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
     </row>
-    <row r="12" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="E12" s="9">
         <v>1132</v>
@@ -1681,7 +1730,7 @@
         <v>0.54</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" s="11">
         <v>1132</v>
@@ -1694,18 +1743,18 @@
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
     </row>
-    <row r="13" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="E13" s="9">
         <v>1478</v>
@@ -1714,7 +1763,7 @@
         <v>2.16</v>
       </c>
       <c r="G13" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H13" s="11">
         <v>1478</v>
@@ -1727,18 +1776,18 @@
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
     </row>
-    <row r="14" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="E14" s="9">
         <v>949</v>
@@ -1747,7 +1796,7 @@
         <v>1.08</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H14" s="11">
         <v>949</v>
@@ -1760,18 +1809,18 @@
       <c r="N14" s="12"/>
       <c r="O14" s="12"/>
     </row>
-    <row r="15" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="E15" s="9">
         <v>697</v>
@@ -1780,7 +1829,7 @@
         <v>0.54</v>
       </c>
       <c r="G15" s="60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H15" s="22">
         <v>697</v>
@@ -1793,14 +1842,14 @@
       <c r="N15" s="23"/>
       <c r="O15" s="23"/>
     </row>
-    <row r="16" spans="1:15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16" s="16">
         <v>7118</v>
@@ -1826,7 +1875,7 @@
     <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -1842,18 +1891,18 @@
       <c r="N17" s="44"/>
       <c r="O17" s="44"/>
     </row>
-    <row r="18" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>12</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="D18" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="E18" s="9">
         <v>907</v>
@@ -1862,7 +1911,7 @@
         <v>0.72</v>
       </c>
       <c r="G18" s="61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H18" s="27">
         <v>907</v>
@@ -1875,18 +1924,18 @@
       <c r="N18" s="43"/>
       <c r="O18" s="43"/>
     </row>
-    <row r="19" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>13</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>47</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>48</v>
       </c>
       <c r="E19" s="9">
         <v>574</v>
@@ -1895,7 +1944,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G19" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H19" s="11">
         <v>574</v>
@@ -1908,18 +1957,18 @@
       <c r="N19" s="12"/>
       <c r="O19" s="12"/>
     </row>
-    <row r="20" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>14</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="E20" s="9">
         <v>746</v>
@@ -1928,7 +1977,7 @@
         <v>0.54</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H20" s="11">
         <v>746</v>
@@ -1941,18 +1990,18 @@
       <c r="N20" s="12"/>
       <c r="O20" s="12"/>
     </row>
-    <row r="21" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>15</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="E21" s="9">
         <v>772</v>
@@ -1961,7 +2010,7 @@
         <v>0.54</v>
       </c>
       <c r="G21" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H21" s="11">
         <v>772</v>
@@ -1974,18 +2023,18 @@
       <c r="N21" s="12"/>
       <c r="O21" s="12"/>
     </row>
-    <row r="22" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>16</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="E22" s="9">
         <v>972</v>
@@ -1994,7 +2043,7 @@
         <v>0.72</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="18">
@@ -2007,18 +2056,18 @@
       <c r="N22" s="12"/>
       <c r="O22" s="12"/>
     </row>
-    <row r="23" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>17</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" s="9">
         <v>726</v>
@@ -2027,7 +2076,7 @@
         <v>0.72</v>
       </c>
       <c r="G23" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="18">
@@ -2040,18 +2089,18 @@
       <c r="N23" s="12"/>
       <c r="O23" s="12"/>
     </row>
-    <row r="24" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>18</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="E24" s="9">
         <v>1324</v>
@@ -2060,7 +2109,7 @@
         <v>0.72</v>
       </c>
       <c r="G24" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="18">
@@ -2073,18 +2122,18 @@
       <c r="N24" s="12"/>
       <c r="O24" s="12"/>
     </row>
-    <row r="25" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>19</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="E25" s="9">
         <v>710</v>
@@ -2093,7 +2142,7 @@
         <v>0.36</v>
       </c>
       <c r="G25" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="18">
@@ -2106,18 +2155,18 @@
       <c r="N25" s="12"/>
       <c r="O25" s="12"/>
     </row>
-    <row r="26" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>20</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="E26" s="9">
         <v>934</v>
@@ -2126,7 +2175,7 @@
         <v>0.54</v>
       </c>
       <c r="G26" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="18">
@@ -2139,18 +2188,18 @@
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
     </row>
-    <row r="27" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>21</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E27" s="9">
         <v>1296</v>
@@ -2159,7 +2208,7 @@
         <v>1.98</v>
       </c>
       <c r="G27" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="18">
@@ -2172,18 +2221,18 @@
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
     </row>
-    <row r="28" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>22</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>63</v>
       </c>
       <c r="E28" s="9">
         <v>2387</v>
@@ -2192,7 +2241,7 @@
         <v>2.34</v>
       </c>
       <c r="G28" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="18">
@@ -2205,18 +2254,18 @@
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
     </row>
-    <row r="29" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>23</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>65</v>
       </c>
       <c r="E29" s="9">
         <v>675</v>
@@ -2225,7 +2274,7 @@
         <v>0.36</v>
       </c>
       <c r="G29" s="63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H29" s="23"/>
       <c r="I29" s="24">
@@ -2238,14 +2287,14 @@
       <c r="N29" s="23"/>
       <c r="O29" s="23"/>
     </row>
-    <row r="30" spans="1:15" ht="15.75" collapsed="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30" s="16">
         <v>12024</v>
@@ -2276,7 +2325,7 @@
     <row r="31" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -2292,18 +2341,18 @@
       <c r="N31" s="44"/>
       <c r="O31" s="44"/>
     </row>
-    <row r="32" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>24</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="D32" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="E32" s="9">
         <v>1065</v>
@@ -2312,7 +2361,7 @@
         <v>1.98</v>
       </c>
       <c r="G32" s="58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H32" s="43"/>
       <c r="I32" s="28">
@@ -2325,18 +2374,18 @@
       <c r="N32" s="43"/>
       <c r="O32" s="43"/>
     </row>
-    <row r="33" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>25</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E33" s="9">
         <v>580</v>
@@ -2345,7 +2394,7 @@
         <v>0.08</v>
       </c>
       <c r="G33" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="18">
@@ -2358,18 +2407,18 @@
       <c r="N33" s="12"/>
       <c r="O33" s="12"/>
     </row>
-    <row r="34" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>26</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E34" s="9">
         <v>876</v>
@@ -2378,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="18">
@@ -2391,18 +2440,18 @@
       <c r="N34" s="12"/>
       <c r="O34" s="12"/>
     </row>
-    <row r="35" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>27</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="E35" s="9">
         <v>1042</v>
@@ -2411,7 +2460,7 @@
         <v>1.62</v>
       </c>
       <c r="G35" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="18">
@@ -2424,18 +2473,18 @@
       <c r="N35" s="12"/>
       <c r="O35" s="12"/>
     </row>
-    <row r="36" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>28</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="E36" s="9">
         <v>661</v>
@@ -2444,7 +2493,7 @@
         <v>0.36</v>
       </c>
       <c r="G36" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="18">
@@ -2457,18 +2506,18 @@
       <c r="N36" s="12"/>
       <c r="O36" s="12"/>
     </row>
-    <row r="37" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>29</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E37" s="9">
         <v>577</v>
@@ -2477,7 +2526,7 @@
         <v>0.09</v>
       </c>
       <c r="G37" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="18">
@@ -2490,18 +2539,18 @@
       <c r="N37" s="12"/>
       <c r="O37" s="12"/>
     </row>
-    <row r="38" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>30</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="E38" s="9">
         <v>919</v>
@@ -2510,7 +2559,7 @@
         <v>0.9</v>
       </c>
       <c r="G38" s="63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H38" s="23"/>
       <c r="I38" s="24">
@@ -2523,14 +2572,14 @@
       <c r="N38" s="23"/>
       <c r="O38" s="23"/>
     </row>
-    <row r="39" spans="1:15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E39" s="16">
         <v>5720</v>
@@ -2556,7 +2605,7 @@
     <row r="40" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -2572,18 +2621,18 @@
       <c r="N40" s="44"/>
       <c r="O40" s="44"/>
     </row>
-    <row r="41" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>31</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="D41" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>87</v>
       </c>
       <c r="E41" s="9">
         <v>1674</v>
@@ -2592,7 +2641,7 @@
         <v>2.7</v>
       </c>
       <c r="G41" s="61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H41" s="43"/>
       <c r="I41" s="28">
@@ -2605,18 +2654,18 @@
       <c r="N41" s="43"/>
       <c r="O41" s="43"/>
     </row>
-    <row r="42" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>32</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="E42" s="9">
         <v>1559</v>
@@ -2625,7 +2674,7 @@
         <v>3.06</v>
       </c>
       <c r="G42" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
@@ -2638,18 +2687,18 @@
       <c r="N42" s="20"/>
       <c r="O42" s="12"/>
     </row>
-    <row r="43" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>33</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E43" s="9">
         <v>918</v>
@@ -2658,7 +2707,7 @@
         <v>0.72</v>
       </c>
       <c r="G43" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
@@ -2671,18 +2720,18 @@
       <c r="N43" s="20"/>
       <c r="O43" s="12"/>
     </row>
-    <row r="44" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>34</v>
       </c>
       <c r="B44" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="E44" s="9">
         <v>1064</v>
@@ -2691,7 +2740,7 @@
         <v>0.72</v>
       </c>
       <c r="G44" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
@@ -2704,18 +2753,18 @@
       <c r="N44" s="20"/>
       <c r="O44" s="12"/>
     </row>
-    <row r="45" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>35</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E45" s="9">
         <v>1240</v>
@@ -2724,7 +2773,7 @@
         <v>1.26</v>
       </c>
       <c r="G45" s="63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45" s="23"/>
       <c r="I45" s="23"/>
@@ -2737,14 +2786,14 @@
       <c r="N45" s="25"/>
       <c r="O45" s="23"/>
     </row>
-    <row r="46" spans="1:15" ht="15.75" collapsed="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
       <c r="B46" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C46" s="13"/>
       <c r="D46" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E46" s="16">
         <v>6455</v>
@@ -2775,7 +2824,7 @@
     <row r="47" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -2791,18 +2840,18 @@
       <c r="N47" s="38"/>
       <c r="O47" s="44"/>
     </row>
-    <row r="48" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>36</v>
       </c>
       <c r="B48" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="D48" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E48" s="9">
         <v>781</v>
@@ -2811,7 +2860,7 @@
         <v>0.54</v>
       </c>
       <c r="G48" s="58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H48" s="43"/>
       <c r="I48" s="43"/>
@@ -2824,18 +2873,18 @@
       <c r="N48" s="29"/>
       <c r="O48" s="43"/>
     </row>
-    <row r="49" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
         <v>37</v>
       </c>
       <c r="B49" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="E49" s="9">
         <v>744</v>
@@ -2844,7 +2893,7 @@
         <v>0.36</v>
       </c>
       <c r="G49" s="63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49" s="23"/>
       <c r="I49" s="23"/>
@@ -2857,14 +2906,14 @@
       <c r="N49" s="25"/>
       <c r="O49" s="23"/>
     </row>
-    <row r="50" spans="1:15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
       <c r="B50" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E50" s="16">
         <v>1525</v>
@@ -2890,7 +2939,7 @@
     <row r="51" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -2906,18 +2955,18 @@
       <c r="N51" s="38"/>
       <c r="O51" s="44"/>
     </row>
-    <row r="52" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>38</v>
       </c>
       <c r="B52" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="D52" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E52" s="9">
         <v>774</v>
@@ -2926,7 +2975,7 @@
         <v>0.54</v>
       </c>
       <c r="G52" s="58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H52" s="43"/>
       <c r="I52" s="43"/>
@@ -2939,18 +2988,18 @@
       <c r="N52" s="29"/>
       <c r="O52" s="12"/>
     </row>
-    <row r="53" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>39</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="E53" s="9">
         <v>1691</v>
@@ -2959,7 +3008,7 @@
         <v>3.6</v>
       </c>
       <c r="G53" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="12"/>
@@ -2972,18 +3021,18 @@
       <c r="N53" s="20"/>
       <c r="O53" s="12"/>
     </row>
-    <row r="54" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>40</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E54" s="9">
         <v>657</v>
@@ -2992,7 +3041,7 @@
         <v>0.54</v>
       </c>
       <c r="G54" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
@@ -3005,18 +3054,18 @@
       <c r="N54" s="20"/>
       <c r="O54" s="12"/>
     </row>
-    <row r="55" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>41</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E55" s="9">
         <v>644</v>
@@ -3025,7 +3074,7 @@
         <v>0.54</v>
       </c>
       <c r="G55" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="12"/>
@@ -3038,18 +3087,18 @@
       <c r="N55" s="20"/>
       <c r="O55" s="12"/>
     </row>
-    <row r="56" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>42</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E56" s="9">
         <v>742</v>
@@ -3058,7 +3107,7 @@
         <v>0.1</v>
       </c>
       <c r="G56" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
@@ -3071,18 +3120,18 @@
       <c r="N56" s="20"/>
       <c r="O56" s="12"/>
     </row>
-    <row r="57" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E57" s="9">
         <v>752</v>
@@ -3091,7 +3140,7 @@
         <v>0.54</v>
       </c>
       <c r="G57" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="12"/>
@@ -3104,18 +3153,18 @@
       <c r="N57" s="20"/>
       <c r="O57" s="12"/>
     </row>
-    <row r="58" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>44</v>
       </c>
       <c r="B58" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="E58" s="9">
         <v>756</v>
@@ -3124,7 +3173,7 @@
         <v>0.9</v>
       </c>
       <c r="G58" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H58" s="12"/>
       <c r="I58" s="12"/>
@@ -3137,18 +3186,18 @@
       <c r="N58" s="20"/>
       <c r="O58" s="12"/>
     </row>
-    <row r="59" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>45</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>115</v>
       </c>
       <c r="E59" s="9">
         <v>596</v>
@@ -3157,7 +3206,7 @@
         <v>0.18</v>
       </c>
       <c r="G59" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="12"/>
@@ -3170,18 +3219,18 @@
       <c r="N59" s="20"/>
       <c r="O59" s="12"/>
     </row>
-    <row r="60" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>46</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E60" s="9">
         <v>640</v>
@@ -3190,7 +3239,7 @@
         <v>0.15</v>
       </c>
       <c r="G60" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
@@ -3203,18 +3252,18 @@
       <c r="N60" s="20"/>
       <c r="O60" s="12"/>
     </row>
-    <row r="61" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>47</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D61" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="E61" s="9">
         <v>1963</v>
@@ -3223,7 +3272,7 @@
         <v>2.52</v>
       </c>
       <c r="G61" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H61" s="12"/>
       <c r="I61" s="12"/>
@@ -3236,18 +3285,18 @@
       <c r="N61" s="20"/>
       <c r="O61" s="12"/>
     </row>
-    <row r="62" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>48</v>
       </c>
       <c r="B62" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D62" s="8" t="s">
         <v>119</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>120</v>
       </c>
       <c r="E62" s="9">
         <v>772</v>
@@ -3256,7 +3305,7 @@
         <v>0.9</v>
       </c>
       <c r="G62" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H62" s="12"/>
       <c r="I62" s="12"/>
@@ -3269,18 +3318,18 @@
       <c r="N62" s="20"/>
       <c r="O62" s="12"/>
     </row>
-    <row r="63" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>49</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E63" s="9">
         <v>557</v>
@@ -3289,7 +3338,7 @@
         <v>0.16</v>
       </c>
       <c r="G63" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
@@ -3302,18 +3351,18 @@
       <c r="N63" s="20"/>
       <c r="O63" s="12"/>
     </row>
-    <row r="64" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>50</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E64" s="9">
         <v>939</v>
@@ -3322,7 +3371,7 @@
         <v>0.72</v>
       </c>
       <c r="G64" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H64" s="12"/>
       <c r="I64" s="12"/>
@@ -3335,18 +3384,18 @@
       <c r="N64" s="12"/>
       <c r="O64" s="21"/>
     </row>
-    <row r="65" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>51</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E65" s="9">
         <v>692</v>
@@ -3355,7 +3404,7 @@
         <v>0.36</v>
       </c>
       <c r="G65" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
@@ -3368,18 +3417,18 @@
       <c r="N65" s="12"/>
       <c r="O65" s="21"/>
     </row>
-    <row r="66" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>52</v>
       </c>
       <c r="B66" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66" s="8" t="s">
         <v>124</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>125</v>
       </c>
       <c r="E66" s="9">
         <v>965</v>
@@ -3388,7 +3437,7 @@
         <v>0.9</v>
       </c>
       <c r="G66" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H66" s="12"/>
       <c r="I66" s="12"/>
@@ -3401,18 +3450,18 @@
       <c r="N66" s="12"/>
       <c r="O66" s="21"/>
     </row>
-    <row r="67" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>53</v>
       </c>
       <c r="B67" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D67" s="8" t="s">
         <v>126</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>127</v>
       </c>
       <c r="E67" s="9">
         <v>1069</v>
@@ -3421,7 +3470,7 @@
         <v>0.72</v>
       </c>
       <c r="G67" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
@@ -3434,18 +3483,18 @@
       <c r="N67" s="12"/>
       <c r="O67" s="21"/>
     </row>
-    <row r="68" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>54</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E68" s="9">
         <v>568</v>
@@ -3454,7 +3503,7 @@
         <v>0.36</v>
       </c>
       <c r="G68" s="63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H68" s="23"/>
       <c r="I68" s="23"/>
@@ -3467,14 +3516,14 @@
       <c r="N68" s="23"/>
       <c r="O68" s="26"/>
     </row>
-    <row r="69" spans="1:15" ht="15.75" collapsed="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="13"/>
       <c r="B69" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C69" s="13"/>
       <c r="D69" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E69" s="16">
         <v>14777</v>
@@ -3505,7 +3554,7 @@
     <row r="70" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
       <c r="B70" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -3521,18 +3570,18 @@
       <c r="N70" s="44"/>
       <c r="O70" s="41"/>
     </row>
-    <row r="71" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>55</v>
       </c>
       <c r="B71" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>133</v>
-      </c>
       <c r="D71" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E71" s="9">
         <v>652</v>
@@ -3541,7 +3590,7 @@
         <v>0.36</v>
       </c>
       <c r="G71" s="61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H71" s="43"/>
       <c r="I71" s="43"/>
@@ -3554,18 +3603,18 @@
       <c r="N71" s="43"/>
       <c r="O71" s="30"/>
     </row>
-    <row r="72" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>56</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E72" s="9">
         <v>678</v>
@@ -3574,7 +3623,7 @@
         <v>0.72</v>
       </c>
       <c r="G72" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H72" s="12"/>
       <c r="I72" s="12"/>
@@ -3587,18 +3636,18 @@
       <c r="N72" s="12"/>
       <c r="O72" s="21"/>
     </row>
-    <row r="73" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>57</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E73" s="9">
         <v>600</v>
@@ -3607,7 +3656,7 @@
         <v>0.17</v>
       </c>
       <c r="G73" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
@@ -3620,18 +3669,18 @@
       <c r="N73" s="12"/>
       <c r="O73" s="21"/>
     </row>
-    <row r="74" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
         <v>58</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E74" s="9">
         <v>577</v>
@@ -3640,7 +3689,7 @@
         <v>0.1</v>
       </c>
       <c r="G74" s="60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H74" s="23"/>
       <c r="I74" s="23"/>
@@ -3653,14 +3702,14 @@
       <c r="N74" s="23"/>
       <c r="O74" s="26"/>
     </row>
-    <row r="75" spans="1:15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="13"/>
       <c r="B75" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C75" s="13"/>
       <c r="D75" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E75" s="16">
         <v>2506</v>
@@ -3686,7 +3735,7 @@
     <row r="76" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -3702,18 +3751,18 @@
       <c r="N76" s="44"/>
       <c r="O76" s="41"/>
     </row>
-    <row r="77" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>59</v>
       </c>
       <c r="B77" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C77" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C77" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="D77" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E77" s="9">
         <v>952</v>
@@ -3722,7 +3771,7 @@
         <v>1.08</v>
       </c>
       <c r="G77" s="61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H77" s="43"/>
       <c r="I77" s="43"/>
@@ -3735,18 +3784,18 @@
       <c r="N77" s="43"/>
       <c r="O77" s="30"/>
     </row>
-    <row r="78" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>60</v>
       </c>
       <c r="B78" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D78" s="8" t="s">
         <v>142</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>143</v>
       </c>
       <c r="E78" s="9">
         <v>1314</v>
@@ -3755,7 +3804,7 @@
         <v>1.98</v>
       </c>
       <c r="G78" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
@@ -3768,18 +3817,18 @@
       <c r="N78" s="12"/>
       <c r="O78" s="21"/>
     </row>
-    <row r="79" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>61</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E79" s="9">
         <v>865</v>
@@ -3788,7 +3837,7 @@
         <v>0.18</v>
       </c>
       <c r="G79" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
@@ -3801,18 +3850,18 @@
       <c r="N79" s="12"/>
       <c r="O79" s="21"/>
     </row>
-    <row r="80" spans="1:15" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>62</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E80" s="9">
         <v>592</v>
@@ -3821,7 +3870,7 @@
         <v>0.08</v>
       </c>
       <c r="G80" s="59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
@@ -3834,18 +3883,18 @@
       <c r="N80" s="12"/>
       <c r="O80" s="21"/>
     </row>
-    <row r="81" spans="1:16" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
         <v>63</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E81" s="9">
         <v>795</v>
@@ -3854,7 +3903,7 @@
         <v>0.13</v>
       </c>
       <c r="G81" s="60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H81" s="23"/>
       <c r="I81" s="23"/>
@@ -3867,14 +3916,14 @@
       <c r="N81" s="23"/>
       <c r="O81" s="26"/>
     </row>
-    <row r="82" spans="1:16" ht="15.75" collapsed="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="13"/>
       <c r="B82" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C82" s="13"/>
       <c r="D82" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E82" s="16">
         <v>4518</v>
@@ -3901,11 +3950,11 @@
     <row r="84" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="49"/>
       <c r="B84" s="50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C84" s="49"/>
       <c r="D84" s="51" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E84" s="52">
         <v>61313</v>
@@ -3946,7 +3995,7 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -3959,6 +4008,17 @@
   </sheetData>
   <autoFilter ref="A1:K86" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF475806-CE1D-4B96-8CDF-DE4BA5FDCDF9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>